--- a/data/GLD_lithic_data.xlsx
+++ b/data/GLD_lithic_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Geluo_cave_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613DD10A-AC92-4A10-A2BD-F245E44E181A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06832509-5041-470D-9DD6-3E5122A9C10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="30936" windowHeight="18696" firstSheet="1" activeTab="1" xr2:uid="{813B3528-8EB7-4C50-AFE6-E9E25DACE1C9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" firstSheet="1" activeTab="1" xr2:uid="{813B3528-8EB7-4C50-AFE6-E9E25DACE1C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Core" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="442">
   <si>
     <t>Layer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1495,6 +1495,18 @@
   </si>
   <si>
     <t>Pointed</t>
+  </si>
+  <si>
+    <t>Centripetal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kombewa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Indeterminate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5974,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="8" t="s">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="X30" s="8" t="s">
         <v>189</v>
@@ -10490,7 +10502,7 @@
         <v>1</v>
       </c>
       <c r="W88" s="8" t="s">
-        <v>379</v>
+        <v>441</v>
       </c>
       <c r="X88" s="8" t="s">
         <v>189</v>
@@ -11660,7 +11672,7 @@
         <v>5</v>
       </c>
       <c r="W103" s="8" t="s">
-        <v>376</v>
+        <v>439</v>
       </c>
       <c r="X103" s="8" t="s">
         <v>189</v>
